--- a/data/trans_orig/IP12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>14854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>25717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92104</t>
+          <t>91317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100944</t>
+          <t>100722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106643</t>
+          <t>105854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115916</t>
+          <t>116037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201880</t>
+          <t>201834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214640</t>
+          <t>214554</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23288</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>28013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27855</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229917</t>
+          <t>230287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>242338</t>
+          <t>242593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225672</t>
+          <t>225743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239485</t>
+          <t>239655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>460734</t>
+          <t>460206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479106</t>
+          <t>479597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111039</t>
+          <t>109959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>121374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125625</t>
+          <t>125764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135883</t>
+          <t>135764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240603</t>
+          <t>240651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254757</t>
+          <t>254753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180376</t>
+          <t>180741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189468</t>
+          <t>190127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>193088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202196</t>
+          <t>202106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377050</t>
+          <t>377285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389658</t>
+          <t>390288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>58690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76515</t>
+          <t>78269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107244</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>625973</t>
+          <t>625465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646732</t>
+          <t>646656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>664779</t>
+          <t>664010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>684670</t>
+          <t>685179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296477</t>
+          <t>1296324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1327206</t>
+          <t>1325452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>41209</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121348</t>
+          <t>121335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134828</t>
+          <t>134863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125824</t>
+          <t>125722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137586</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251727</t>
+          <t>251542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269113</t>
+          <t>269363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28095</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35714</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57961</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>208155</t>
+          <t>207580</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222451</t>
+          <t>221858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234973</t>
+          <t>234851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251693</t>
+          <t>250594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>449144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469527</t>
+          <t>470676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>32936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>136680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148286</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141909</t>
+          <t>141185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152978</t>
+          <t>152854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>282678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298278</t>
+          <t>298047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156406</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165942</t>
+          <t>166060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158131</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170494</t>
+          <t>169992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318211</t>
+          <t>318417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334136</t>
+          <t>334176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>49428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74651</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76314</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107969</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145150</t>
+          <t>144490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636740</t>
+          <t>636543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>661204</t>
+          <t>661963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677193</t>
+          <t>676153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>700737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319748</t>
+          <t>1320408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356929</t>
+          <t>1356943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113982</t>
+          <t>114084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124642</t>
+          <t>124146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111727</t>
+          <t>111444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120338</t>
+          <t>119979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229451</t>
+          <t>229025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242624</t>
+          <t>242285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>32151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>52525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178787</t>
+          <t>178366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193760</t>
+          <t>193332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231203</t>
+          <t>231321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244935</t>
+          <t>245469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416198</t>
+          <t>416053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434883</t>
+          <t>434584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170082</t>
+          <t>169817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181271</t>
+          <t>181640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167178</t>
+          <t>167815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179756</t>
+          <t>179556</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341696</t>
+          <t>341953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358818</t>
+          <t>358763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24770</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157989</t>
+          <t>158285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167853</t>
+          <t>167920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158583</t>
+          <t>160208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169873</t>
+          <t>169995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321961</t>
+          <t>322608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335705</t>
+          <t>335866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636050</t>
+          <t>635728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659178</t>
+          <t>659135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683818</t>
+          <t>684485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>706018</t>
+          <t>706550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1327057</t>
+          <t>1327141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1358329</t>
+          <t>1359506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51211</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>58716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103068</t>
+          <t>103561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112842</t>
+          <t>112746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139881</t>
+          <t>139520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150535</t>
+          <t>150943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159564</t>
+          <t>159158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171952</t>
+          <t>171887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303753</t>
+          <t>303445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320607</t>
+          <t>319677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21821</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41163</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151344</t>
+          <t>150109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163998</t>
+          <t>163630</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>190366</t>
+          <t>189789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203527</t>
+          <t>203347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>344400</t>
+          <t>345589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363742</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48999</t>
+          <t>51430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253860</t>
+          <t>253456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266519</t>
+          <t>266867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271097</t>
+          <t>271137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291103</t>
+          <t>290897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531941</t>
+          <t>529510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>554419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>58539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127135</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9323</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5370</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15170</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9132</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14854</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5045</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14300</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9323</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5343</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15526</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>112057</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>106210</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116010</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>97039</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>91317</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>100722</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>91871</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101126</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>112057</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>105854</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>116037</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201834</t>
+          <t>201932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214554</t>
+          <t>214788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14817</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28176</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16058</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10612</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22918</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23562</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20308</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14101</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28013</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>46428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233448</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>225580</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>238939</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>354</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>237147</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>230287</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>242593</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229643</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>242217</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>233448</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>225743</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>239655</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>460206</t>
+          <t>460533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479597</t>
+          <t>480126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>9968</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15914</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>10743</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6174</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17589</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16979</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5751</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15751</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131547</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>125601</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>136079</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>116805</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>109959</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>121374</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>110569</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121063</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131547</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>125764</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135764</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240651</t>
+          <t>239871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254753</t>
+          <t>255096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4482</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>7945</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13356</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13450</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7793</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12961</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192524</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201567</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>186152</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>180741</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190127</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>180647</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189948</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>198256</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>193088</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202106</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377285</t>
+          <t>377593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390288</t>
+          <t>389716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37145</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58298</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34365</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55556</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34308</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37521</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58690</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78269</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107397</t>
+          <t>106506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>675308</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>664402</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>685555</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>637143</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>625465</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646656</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>625509</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>646713</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>675308</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>664010</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>685179</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296324</t>
+          <t>1297215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325452</t>
+          <t>1327300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13234</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7841</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19662</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>17965</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11898</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25426</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12178</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24554</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13234</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20268</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23388</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41209</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>132756</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>126328</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>138149</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128796</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>121335</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>134863</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>122207</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>134583</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>132756</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>125722</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>138050</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251542</t>
+          <t>251454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>269363</t>
+          <t>269599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,107 +3013,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25118</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17985</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20242</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14392</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28670</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13464</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>28020</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25118</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18397</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34140</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>45359</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>34563</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>57948</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>6,84%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>45359</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>34565</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>56097</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>243873</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>234259</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>251006</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>216008</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207580</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>221858</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>208230</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>222786</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>243873</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>234851</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250594</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449144</t>
+          <t>447293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>470676</t>
+          <t>470678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10222</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5779</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16367</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14011</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8579</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20363</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20859</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10222</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5717</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17386</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>32281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148349</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142204</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152792</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143032</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>136680</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148464</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136184</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148135</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148349</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141185</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>152854</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>282678</t>
+          <t>283333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298047</t>
+          <t>299041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9769</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22334</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9074</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5277</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14976</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15269</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9963</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22616</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>164969</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>157621</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170186</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162263</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156361</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>166060</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156068</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166514</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>164969</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>157339</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169992</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318417</t>
+          <t>318767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334176</t>
+          <t>333799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51375</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49428</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>74848</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50093</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52770</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77354</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>109361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144490</t>
+          <t>146480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689947</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>676120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>702132</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>937</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>650099</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>636543</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>637589</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>661298</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689947</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>676153</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>700737</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1320408</t>
+          <t>1318418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356943</t>
+          <t>1355537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3927</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12713</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11866</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7508</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17570</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7637</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18614</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7395</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4185</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12720</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26793</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>116769</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>111451</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>119788</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>114084</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>124146</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>113040</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>124017</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>116769</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>111444</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>119979</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,04%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229025</t>
+          <t>229272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242285</t>
+          <t>242362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12119</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26118</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>23323</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17185</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32151</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17305</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31068</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18872</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12592</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26740</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52525</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>239189</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231943</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>245942</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>187194</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178366</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>193332</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>179449</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>193212</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,92%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>239189</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>231321</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>245469</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416053</t>
+          <t>415358</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434584</t>
+          <t>435490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8751</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21108</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12028</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19082</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7119</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18396</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14044</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9016</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20757</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>174528</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167464</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>179821</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>176871</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>169817</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>181640</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>170503</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>181780</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>174528</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167815</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>179556</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341953</t>
+          <t>341089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358763</t>
+          <t>358495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14300</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8509</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4763</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14398</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14193</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4053</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13840</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>165877</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>159748</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169895</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>164174</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>158285</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167920</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>158490</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>168033</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>165877</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>160208</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>169995</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>322608</t>
+          <t>322520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335866</t>
+          <t>335968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172683</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172683</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172683</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37665</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59976</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>44619</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>43970</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>67739</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38294</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60359</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>87932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>696362</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684868</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>707179</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>975</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>648028</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>635728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659135</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>636015</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>659784</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>696362</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>684485</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>706550</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1327141</t>
+          <t>1327442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1359506</t>
+          <t>1360666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703754</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42216</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48322</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>52936</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49213</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55338</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51297</t>
+          <t>44340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58716</t>
+          <t>49939</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>108836</t>
+          <t>93987</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103561</t>
+          <t>88592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112746</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13897</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9416</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21733</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13265</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8356</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19779</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29303</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>143625</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135789</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>148106</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>146034</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>139520</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>150943</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>166517</t>
+          <t>133170</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159158</t>
+          <t>127143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171887</t>
+          <t>137458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>312550</t>
+          <t>276794</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303445</t>
+          <t>268947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>319677</t>
+          <t>283488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14509</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8873</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21655</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14863</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9442</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22963</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29738</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>40309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>185617</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>191253</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>158209</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150109</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>163630</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>197615</t>
+          <t>159641</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189789</t>
+          <t>152120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203347</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>355825</t>
+          <t>345258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>345589</t>
+          <t>334489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>353456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22509</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14684</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33818</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14568</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8591</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22002</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22647</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51430</t>
+          <t>49446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>270136</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>258827</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>277961</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>260890</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>253456</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>266867</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>282836</t>
+          <t>241434</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271137</t>
+          <t>234127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>290897</t>
+          <t>246502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>543725</t>
+          <t>511570</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529510</t>
+          <t>499752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554419</t>
+          <t>521974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70112</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>37016</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58539</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>36345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125932</t>
+          <t>120273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>865</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>618068</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>606801</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>628324</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>582184</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>569808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1320937</t>
+          <t>1227609</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1301380</t>
+          <t>1209389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337289</t>
+          <t>1243691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
